--- a/Excels/PresetLayerOpinionSheet.xlsx
+++ b/Excels/PresetLayerOpinionSheet.xlsx
@@ -66,11 +66,11 @@
     <font>
       <name val="Meiryo"/>
       <i val="1"/>
-      <color rgb="009CA3AF"/>
+      <color rgb="004B5563"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +117,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1D5DB"/>
+        <bgColor rgb="00D1D5DB"/>
       </patternFill>
     </fill>
   </fills>
@@ -172,7 +178,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>

--- a/Excels/PresetLayerOpinionSheet.xlsx
+++ b/Excels/PresetLayerOpinionSheet.xlsx
@@ -684,7 +684,7 @@
         <v>--- GENERATOR CUSTOM PARAMETERS (各レイヤー固有設定) ---</v>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
+    <row r="6">
       <c r="A6" t="str">
         <v>Generator</v>
       </c>
@@ -700,9 +700,8 @@
       <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6" t="str" xml:space="preserve">
-        <v xml:space="preserve">200以上は極端になる。
-画面を覆いすぎると近すぎて良く分からなくなるので大きさには気を付けたい</v>
+      <c r="F6" t="str">
+        <v>200以上は極端になる。画面を覆いすぎると近すぎて良く分からなくなるので大きさには気を付けたい</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -17141,9 +17140,8 @@
       <c r="E88">
         <v>5</v>
       </c>
-      <c r="F88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Frequencyと連動すると
-面白い効果が得られやすい</v>
+      <c r="F88" t="str">
+        <v>Frequencyと連動すると面白い効果が得られやすい</v>
       </c>
       <c r="G88">
         <v>5</v>
@@ -18149,9 +18147,8 @@
       <c r="E93">
         <v>5</v>
       </c>
-      <c r="F93" t="str" xml:space="preserve">
-        <v xml:space="preserve">固定値より積極的に
-変動して使うのが良い</v>
+      <c r="F93" t="str">
+        <v>固定値より積極的に変動して使うのが良い</v>
       </c>
       <c r="G93">
         <v>3</v>
@@ -19540,7 +19537,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="100" xml:space="preserve">
+    <row r="100">
       <c r="A100" t="str">
         <v>Generator</v>
       </c>
@@ -19556,10 +19553,8 @@
       <c r="E100">
         <v>3</v>
       </c>
-      <c r="F100" t="str" xml:space="preserve">
-        <v xml:space="preserve">固定なら0.5が無難。
-もしくは変動して一辺に
-偏らないように気を付ける</v>
+      <c r="F100" t="str">
+        <v>固定なら0.5が無難。もしくは変動して一辺に偏らないように気を付ける</v>
       </c>
       <c r="G100">
         <v>2</v>

--- a/Excels/PresetLayerOpinionSheet.xlsx
+++ b/Excels/PresetLayerOpinionSheet.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BN119"/>
+  <dimension ref="A1:BT148"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -478,6 +478,12 @@
       <c r="BL3" t="str">
         <v>Glass Crack</v>
       </c>
+      <c r="BO3" t="str">
+        <v>Dot Design</v>
+      </c>
+      <c r="BR3" t="str">
+        <v>Milky Way</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -678,6 +684,24 @@
       <c r="BN4" t="str">
         <v>Comment</v>
       </c>
+      <c r="BO4" t="str">
+        <v>Score</v>
+      </c>
+      <c r="BP4" t="str">
+        <v>Move</v>
+      </c>
+      <c r="BQ4" t="str">
+        <v>Comment</v>
+      </c>
+      <c r="BR4" t="str">
+        <v>Score</v>
+      </c>
+      <c r="BS4" t="str">
+        <v>Move</v>
+      </c>
+      <c r="BT4" t="str">
+        <v>Comment</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -883,6 +907,24 @@
       <c r="BN6" t="str">
         <v>-</v>
       </c>
+      <c r="BO6" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP6" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ6" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR6" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS6" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT6" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1083,6 +1125,24 @@
       <c r="BN7" t="str">
         <v>-</v>
       </c>
+      <c r="BO7" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP7" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ7" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR7" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS7" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT7" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="8" xml:space="preserve">
       <c r="A8" t="str">
@@ -1284,6 +1344,24 @@
       <c r="BN8" t="str">
         <v>-</v>
       </c>
+      <c r="BO8" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP8" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ8" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR8" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS8" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT8" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1482,6 +1560,24 @@
         <v>-</v>
       </c>
       <c r="BN9" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO9" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP9" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ9" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR9" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS9" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT9" t="str">
         <v>-</v>
       </c>
     </row>
@@ -1686,6 +1782,24 @@
       <c r="BN10" t="str">
         <v>-</v>
       </c>
+      <c r="BO10" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP10" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ10" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR10" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS10" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT10" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1886,6 +2000,24 @@
       <c r="BN11" t="str">
         <v>-</v>
       </c>
+      <c r="BO11" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP11" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ11" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR11" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS11" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT11" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -2086,6 +2218,24 @@
       <c r="BN12" t="str">
         <v>-</v>
       </c>
+      <c r="BO12" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP12" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ12" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR12" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS12" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT12" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -2286,6 +2436,24 @@
       <c r="BN13" t="str">
         <v>-</v>
       </c>
+      <c r="BO13" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP13" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ13" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR13" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS13" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT13" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="14" xml:space="preserve">
       <c r="A14" t="str">
@@ -2487,6 +2655,24 @@
       <c r="BN14" t="str">
         <v>-</v>
       </c>
+      <c r="BO14" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP14" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ14" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR14" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS14" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT14" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -2678,6 +2864,24 @@
       <c r="BK15" t="str">
         <v>-</v>
       </c>
+      <c r="BO15" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP15" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ15" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR15" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS15" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT15" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -2878,6 +3082,24 @@
       <c r="BN16" t="str">
         <v>-</v>
       </c>
+      <c r="BO16" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP16" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ16" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR16" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS16" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT16" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -3078,6 +3300,24 @@
       <c r="BN17" t="str">
         <v>変動も良いが乱数が良く使える</v>
       </c>
+      <c r="BO17" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP17" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ17" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR17" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS17" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT17" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="18" xml:space="preserve">
       <c r="A18" t="str">
@@ -3279,6 +3519,24 @@
         <v xml:space="preserve">変動も良いが乱数が良く使える
 ヒビ毎に変化あるとなお良い</v>
       </c>
+      <c r="BO18" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP18" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ18" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR18" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS18" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT18" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -3477,6 +3735,24 @@
         <v>-</v>
       </c>
       <c r="BN19" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO19" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP19" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ19" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR19" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS19" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT19" t="str">
         <v>-</v>
       </c>
     </row>
@@ -3688,6 +3964,24 @@
 変化が等速なのがおかしい
 急激なlog変化量のカーブイメージ</v>
       </c>
+      <c r="BO20">
+        <v>1</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="str">
+        <v>2500, 5000, 10000の3つから固定でよい</v>
+      </c>
+      <c r="BR20" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS20" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT20" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -3888,6 +4182,24 @@
       <c r="BN21" t="str">
         <v>-</v>
       </c>
+      <c r="BO21" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP21" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ21" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR21" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS21" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT21" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -4088,6 +4400,24 @@
       <c r="BN22" t="str">
         <v>-</v>
       </c>
+      <c r="BO22" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP22" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ22" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR22" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS22" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT22" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -4288,6 +4618,24 @@
       <c r="BN23" t="str">
         <v>効果が分かりづらい</v>
       </c>
+      <c r="BO23" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP23" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ23" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR23" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS23" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT23" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -4488,6 +4836,24 @@
       <c r="BN24" t="str">
         <v>-</v>
       </c>
+      <c r="BO24" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP24" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ24" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR24" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS24" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT24" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -4688,6 +5054,24 @@
       <c r="BN25" t="str">
         <v>-</v>
       </c>
+      <c r="BO25" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP25" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ25" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR25" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS25" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT25" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -4888,6 +5272,24 @@
       <c r="BN26" t="str">
         <v>-</v>
       </c>
+      <c r="BO26" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP26" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ26" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR26" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS26" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT26" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -5088,6 +5490,24 @@
       <c r="BN27" t="str">
         <v>-</v>
       </c>
+      <c r="BO27" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP27" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ27" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR27" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS27" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT27" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -5287,6 +5707,24 @@
       </c>
       <c r="BN28" t="str">
         <v>効果はわかるが根本を直したい</v>
+      </c>
+      <c r="BO28" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP28" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ28" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR28" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS28" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT28" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
@@ -5490,6 +5928,24 @@
       <c r="BN29" t="str">
         <v>-</v>
       </c>
+      <c r="BO29" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP29" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ29" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR29" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS29" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT29" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -5690,6 +6146,24 @@
       <c r="BN30" t="str">
         <v>-</v>
       </c>
+      <c r="BO30" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP30" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ30" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR30" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS30" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT30" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -5890,6 +6364,24 @@
       <c r="BN31" t="str">
         <v>-</v>
       </c>
+      <c r="BO31" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP31" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ31" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR31" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS31" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT31" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="32" xml:space="preserve">
       <c r="A32" t="str">
@@ -6089,6 +6581,24 @@
         <v>-</v>
       </c>
       <c r="BN32" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO32" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP32" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ32" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR32" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS32" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT32" t="str">
         <v>-</v>
       </c>
     </row>
@@ -6295,6 +6805,24 @@
       <c r="BN33" t="str">
         <v>-</v>
       </c>
+      <c r="BO33" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP33" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ33" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR33" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS33" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT33" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -6495,6 +7023,24 @@
       <c r="BN34" t="str">
         <v>-</v>
       </c>
+      <c r="BO34" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP34" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ34" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR34" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS34" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT34" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -6695,6 +7241,24 @@
       <c r="BN35" t="str">
         <v>-</v>
       </c>
+      <c r="BO35" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP35" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ35" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR35" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS35" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT35" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="36" xml:space="preserve">
       <c r="A36" t="str">
@@ -6896,6 +7460,24 @@
       <c r="BN36" t="str">
         <v>-</v>
       </c>
+      <c r="BO36" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP36" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ36" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR36" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS36" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT36" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -7096,6 +7678,18 @@
       <c r="BN37" t="str">
         <v>-</v>
       </c>
+      <c r="BO37" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP37" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ37" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -7296,6 +7890,24 @@
       <c r="BN38" t="str">
         <v>効果が分かりづらい</v>
       </c>
+      <c r="BO38" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP38" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ38" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR38" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS38" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT38" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="39" xml:space="preserve">
       <c r="A39" t="str">
@@ -7497,6 +8109,24 @@
       <c r="BN39" t="str">
         <v>-</v>
       </c>
+      <c r="BO39" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP39" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ39" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR39" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS39" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT39" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -7697,6 +8327,24 @@
       <c r="BN40" t="str">
         <v>下手な漫画風で非常にリアルさに欠ける</v>
       </c>
+      <c r="BO40" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP40" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ40" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR40" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS40" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT40" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -7897,6 +8545,24 @@
       <c r="BN41" t="str">
         <v>-</v>
       </c>
+      <c r="BO41" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP41" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ41" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR41" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS41" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT41" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -8097,6 +8763,24 @@
       <c r="BN42" t="str">
         <v>-</v>
       </c>
+      <c r="BO42" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP42" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ42" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR42" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS42" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT42" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="43" xml:space="preserve">
       <c r="A43" t="str">
@@ -8298,6 +8982,24 @@
       <c r="BN43" t="str">
         <v>-</v>
       </c>
+      <c r="BO43" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP43" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ43" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR43" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS43" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT43" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="44" xml:space="preserve">
       <c r="A44" t="str">
@@ -8497,6 +9199,24 @@
         <v>-</v>
       </c>
       <c r="BN44" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO44" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP44" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ44" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR44" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS44" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT44" t="str">
         <v>-</v>
       </c>
     </row>
@@ -8701,6 +9421,24 @@
       <c r="BN45" t="str">
         <v>-</v>
       </c>
+      <c r="BO45" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP45" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ45" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR45" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS45" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT45" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="46" xml:space="preserve">
       <c r="A46" t="str">
@@ -8902,6 +9640,24 @@
       <c r="BN46" t="str">
         <v>効果が分かりづらい</v>
       </c>
+      <c r="BO46" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP46" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ46" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR46" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS46" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT46" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="47" xml:space="preserve">
       <c r="A47" t="str">
@@ -9103,6 +9859,24 @@
       <c r="BN47" t="str">
         <v>-</v>
       </c>
+      <c r="BO47" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP47" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ47" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR47" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS47" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT47" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -9303,6 +10077,24 @@
       <c r="BN48" t="str">
         <v>-</v>
       </c>
+      <c r="BO48" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP48" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ48" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR48" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS48" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT48" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -9503,6 +10295,24 @@
       <c r="BN49" t="str">
         <v>-</v>
       </c>
+      <c r="BO49" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP49" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ49" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR49" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS49" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT49" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="50" xml:space="preserve">
       <c r="A50" t="str">
@@ -9702,6 +10512,24 @@
         <v>-</v>
       </c>
       <c r="BN50" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO50" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP50" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ50" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR50" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS50" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT50" t="str">
         <v>-</v>
       </c>
     </row>
@@ -9907,6 +10735,24 @@
       <c r="BN51" t="str">
         <v>-</v>
       </c>
+      <c r="BO51" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP51" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ51" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR51" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS51" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT51" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -10107,6 +10953,24 @@
       <c r="BN52" t="str">
         <v>-</v>
       </c>
+      <c r="BO52" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP52" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ52" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR52" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS52" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT52" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -10307,6 +11171,24 @@
       <c r="BN53" t="str">
         <v>-</v>
       </c>
+      <c r="BO53" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP53" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ53" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR53" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS53" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT53" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -10507,6 +11389,24 @@
       <c r="BN54" t="str">
         <v>-</v>
       </c>
+      <c r="BO54" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP54" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ54" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR54" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS54" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT54" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -10705,6 +11605,24 @@
         <v>-</v>
       </c>
       <c r="BN55" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO55" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP55" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ55" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR55" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS55" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT55" t="str">
         <v>-</v>
       </c>
     </row>
@@ -10909,6 +11827,24 @@
       <c r="BN56" t="str">
         <v>-</v>
       </c>
+      <c r="BO56" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP56" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ56" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR56" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS56" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT56" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -11109,6 +12045,24 @@
       <c r="BN57" t="str">
         <v>-</v>
       </c>
+      <c r="BO57" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP57" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ57" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR57" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS57" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT57" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -11309,6 +12263,24 @@
       <c r="BN58" t="str">
         <v>-</v>
       </c>
+      <c r="BO58" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP58" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ58" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR58" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS58" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT58" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -11509,6 +12481,24 @@
       <c r="BN59" t="str">
         <v>-</v>
       </c>
+      <c r="BO59" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP59" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ59" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR59" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS59" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT59" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -11709,6 +12699,24 @@
       <c r="BN60" t="str">
         <v>-</v>
       </c>
+      <c r="BO60" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP60" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ60" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR60" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS60" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT60" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="61" xml:space="preserve">
       <c r="A61" t="str">
@@ -11908,6 +12916,24 @@
         <v>-</v>
       </c>
       <c r="BN61" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO61" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP61" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ61" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR61" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS61" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT61" t="str">
         <v>-</v>
       </c>
     </row>
@@ -12112,6 +13138,24 @@
       <c r="BN62" t="str">
         <v>-</v>
       </c>
+      <c r="BO62" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP62" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ62" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR62" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS62" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT62" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -12312,6 +13356,24 @@
       <c r="BN63" t="str">
         <v>-</v>
       </c>
+      <c r="BO63" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP63" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ63" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR63" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS63" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT63" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="64" xml:space="preserve">
       <c r="A64" t="str">
@@ -12513,6 +13575,24 @@
       <c r="BN64" t="str">
         <v>-</v>
       </c>
+      <c r="BO64" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP64" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ64" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR64" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS64" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT64" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -12713,6 +13793,24 @@
       <c r="BN65" t="str">
         <v>-</v>
       </c>
+      <c r="BO65" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP65" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ65" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR65" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS65" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT65" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="66" xml:space="preserve">
       <c r="A66" t="str">
@@ -12914,6 +14012,24 @@
       <c r="BN66" t="str">
         <v>-</v>
       </c>
+      <c r="BO66" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP66" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ66" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR66" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS66" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT66" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="67" xml:space="preserve">
       <c r="A67" t="str">
@@ -13115,6 +14231,24 @@
       <c r="BN67" t="str">
         <v>-</v>
       </c>
+      <c r="BO67" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP67" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ67" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR67" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS67" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT67" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="68" xml:space="preserve">
       <c r="A68" t="str">
@@ -13314,6 +14448,24 @@
         <v>-</v>
       </c>
       <c r="BN68" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO68" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP68" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ68" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR68" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS68" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT68" t="str">
         <v>-</v>
       </c>
     </row>
@@ -13518,6 +14670,24 @@
       <c r="BN69" t="str">
         <v>-</v>
       </c>
+      <c r="BO69" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP69" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ69" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR69" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS69" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT69" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="70" xml:space="preserve">
       <c r="A70" t="str">
@@ -13719,6 +14889,24 @@
       <c r="BN70" t="str">
         <v>-</v>
       </c>
+      <c r="BO70" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP70" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ70" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR70" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS70" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT70" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -13919,6 +15107,24 @@
       <c r="BN71" t="str">
         <v>-</v>
       </c>
+      <c r="BO71" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP71" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ71" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR71" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS71" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT71" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -14119,6 +15325,24 @@
       <c r="BN72" t="str">
         <v>-</v>
       </c>
+      <c r="BO72" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP72" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ72" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR72" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS72" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT72" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -14319,6 +15543,24 @@
       <c r="BN73" t="str">
         <v>-</v>
       </c>
+      <c r="BO73" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP73" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ73" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR73" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS73" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT73" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -14519,6 +15761,24 @@
       <c r="BN74" t="str">
         <v>-</v>
       </c>
+      <c r="BO74" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP74" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ74" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR74" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS74" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT74" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -14719,6 +15979,24 @@
       <c r="BN75" t="str">
         <v>-</v>
       </c>
+      <c r="BO75" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP75" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ75" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR75" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS75" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT75" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -14919,6 +16197,24 @@
       <c r="BN76" t="str">
         <v>-</v>
       </c>
+      <c r="BO76" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP76" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ76" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR76" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS76" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT76" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -15119,6 +16415,24 @@
       <c r="BN77" t="str">
         <v>-</v>
       </c>
+      <c r="BO77" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP77" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ77" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR77" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS77" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT77" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -15319,6 +16633,24 @@
       <c r="BN78" t="str">
         <v>-</v>
       </c>
+      <c r="BO78" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP78" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ78" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR78" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS78" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT78" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -15519,6 +16851,24 @@
       <c r="BN79" t="str">
         <v>-</v>
       </c>
+      <c r="BO79" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP79" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ79" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR79" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS79" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT79" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="80" xml:space="preserve">
       <c r="A80" t="str">
@@ -15720,6 +17070,24 @@
       <c r="BN80" t="str">
         <v>-</v>
       </c>
+      <c r="BO80" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP80" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ80" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR80" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS80" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT80" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -15920,6 +17288,24 @@
       <c r="BN81" t="str">
         <v>-</v>
       </c>
+      <c r="BO81" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP81" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ81" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR81" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS81" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT81" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -16120,6 +17506,24 @@
       <c r="BN82" t="str">
         <v>-</v>
       </c>
+      <c r="BO82" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP82" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ82" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR82" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS82" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT82" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -16320,6 +17724,24 @@
       <c r="BN83" t="str">
         <v>-</v>
       </c>
+      <c r="BO83" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP83" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ83" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR83" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS83" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT83" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -16520,6 +17942,24 @@
       <c r="BN84" t="str">
         <v>-</v>
       </c>
+      <c r="BO84" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP84" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ84" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR84" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS84" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT84" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="85" xml:space="preserve">
       <c r="A85" t="str">
@@ -16721,6 +18161,24 @@
       <c r="BN85" t="str">
         <v>-</v>
       </c>
+      <c r="BO85" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP85" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ85" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR85" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS85" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT85" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -16919,6 +18377,24 @@
         <v>-</v>
       </c>
       <c r="BN86" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO86" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP86" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ86" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR86" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS86" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT86" t="str">
         <v>-</v>
       </c>
     </row>
@@ -17123,6 +18599,24 @@
       <c r="BN87" t="str">
         <v>-</v>
       </c>
+      <c r="BO87" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP87" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ87" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR87" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS87" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT87" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="88" xml:space="preserve">
       <c r="A88" t="str">
@@ -17324,6 +18818,24 @@
       <c r="BN88" t="str">
         <v>-</v>
       </c>
+      <c r="BO88" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP88" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ88" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR88" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS88" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT88" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -17522,6 +19034,24 @@
         <v>-</v>
       </c>
       <c r="BN89" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO89" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP89" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ89" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR89" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS89" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT89" t="str">
         <v>-</v>
       </c>
     </row>
@@ -17726,6 +19256,24 @@
       <c r="BN90" t="str">
         <v>-</v>
       </c>
+      <c r="BO90" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP90" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ90" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR90" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS90" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT90" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="91" xml:space="preserve">
       <c r="A91" t="str">
@@ -17928,6 +19476,24 @@
       <c r="BN91" t="str">
         <v>-</v>
       </c>
+      <c r="BO91">
+        <v>5</v>
+      </c>
+      <c r="BP91">
+        <v>0</v>
+      </c>
+      <c r="BQ91" t="str">
+        <v/>
+      </c>
+      <c r="BR91" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS91" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT91" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="92" xml:space="preserve">
       <c r="A92" t="str">
@@ -18130,6 +19696,24 @@
       <c r="BN92" t="str">
         <v>-</v>
       </c>
+      <c r="BO92" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP92" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ92" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR92" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS92" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT92" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="93" xml:space="preserve">
       <c r="A93" t="str">
@@ -18334,6 +19918,24 @@
       <c r="BN93" t="str">
         <v>-</v>
       </c>
+      <c r="BO93" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP93" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ93" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR93" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS93" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT93" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -18534,6 +20136,18 @@
       <c r="BN94" t="str">
         <v>-</v>
       </c>
+      <c r="BO94" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP94" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ94" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95" xml:space="preserve">
       <c r="A95" t="str">
@@ -18735,6 +20349,24 @@
       <c r="BN95" t="str">
         <v>-</v>
       </c>
+      <c r="BO95" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP95" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ95" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR95" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS95" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT95" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="96" xml:space="preserve">
       <c r="A96" t="str">
@@ -18936,6 +20568,24 @@
         <v xml:space="preserve">描画がチープ
 また大きなヒビから派生するのが自然なはずだが独立して変化な箇所でヒビ入るからかなり不自然な線がはいるだけのも効果で使い物になっていない</v>
       </c>
+      <c r="BO96" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP96" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ96" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR96" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS96" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT96" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -19136,6 +20786,24 @@
       <c r="BN97" t="str">
         <v>-</v>
       </c>
+      <c r="BO97">
+        <v>1</v>
+      </c>
+      <c r="BP97">
+        <v>0</v>
+      </c>
+      <c r="BQ97" t="str">
+        <v/>
+      </c>
+      <c r="BR97" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS97" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT97" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -19336,6 +21004,24 @@
       <c r="BN98" t="str">
         <v>-</v>
       </c>
+      <c r="BO98" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP98" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ98" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR98" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS98" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT98" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -19536,6 +21222,24 @@
       <c r="BN99" t="str">
         <v>-</v>
       </c>
+      <c r="BO99" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP99" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ99" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR99" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS99" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT99" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -19736,6 +21440,24 @@
       <c r="BN100" t="str">
         <v>-</v>
       </c>
+      <c r="BO100" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP100" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ100" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR100" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS100" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT100" t="str">
+        <v>-</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -19941,6 +21663,18 @@
       <c r="BN102" t="str">
         <v>ランダム色で良い</v>
       </c>
+      <c r="BO102">
+        <v>5</v>
+      </c>
+      <c r="BP102">
+        <v>0</v>
+      </c>
+      <c r="BQ102" t="str">
+        <v/>
+      </c>
+      <c r="BT102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103" xml:space="preserve">
       <c r="A103" t="str">
@@ -20142,6 +21876,18 @@
       <c r="BN103" t="str">
         <v>固定値でも良いが変動しても効果的</v>
       </c>
+      <c r="BO103">
+        <v>5</v>
+      </c>
+      <c r="BP103">
+        <v>5</v>
+      </c>
+      <c r="BQ103" t="str">
+        <v/>
+      </c>
+      <c r="BT103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -20347,6 +22093,18 @@
       <c r="BN105" t="str">
         <v>基本的には0でよい</v>
       </c>
+      <c r="BO105">
+        <v>1</v>
+      </c>
+      <c r="BP105">
+        <v>0</v>
+      </c>
+      <c r="BQ105" t="str">
+        <v>0固定でよい</v>
+      </c>
+      <c r="BT105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -20547,6 +22305,18 @@
       <c r="BN106" t="str">
         <v>基本的には0でよい</v>
       </c>
+      <c r="BO106">
+        <v>1</v>
+      </c>
+      <c r="BP106">
+        <v>0</v>
+      </c>
+      <c r="BQ106" t="str">
+        <v>0固定でよい</v>
+      </c>
+      <c r="BT106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -20747,6 +22517,18 @@
       <c r="BN107" t="str">
         <v>基本0 たまに変わり種としてDuration分をかけて1回転、2回転すると効果的</v>
       </c>
+      <c r="BO107">
+        <v>2</v>
+      </c>
+      <c r="BP107">
+        <v>0</v>
+      </c>
+      <c r="BQ107" t="str">
+        <v>0,45,90,135,180 のいずれか</v>
+      </c>
+      <c r="BT107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -20947,6 +22729,18 @@
       <c r="BN108" t="str">
         <v>1未満は使わない、キーフレーム移動する際はごくゆっくり動くと破綻しない。TIME % が小さいと使いづらい</v>
       </c>
+      <c r="BO108">
+        <v>2</v>
+      </c>
+      <c r="BP108">
+        <v>0</v>
+      </c>
+      <c r="BQ108" t="str">
+        <v/>
+      </c>
+      <c r="BT108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -21147,6 +22941,18 @@
       <c r="BN109" t="str">
         <v>チカチカと目に痛くなるのでほぼ使わない</v>
       </c>
+      <c r="BO109">
+        <v>1</v>
+      </c>
+      <c r="BP109">
+        <v>0</v>
+      </c>
+      <c r="BQ109" t="str">
+        <v/>
+      </c>
+      <c r="BT109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -21347,6 +23153,18 @@
       <c r="BN110" t="str">
         <v>あまり効果がわからないので据え置き(50以上でもっと分かり易くさせても良い)</v>
       </c>
+      <c r="BO110">
+        <v>5</v>
+      </c>
+      <c r="BP110">
+        <v>5</v>
+      </c>
+      <c r="BQ110" t="str">
+        <v/>
+      </c>
+      <c r="BT110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -21547,6 +23365,18 @@
       <c r="BN111" t="str">
         <v>効果的なので高数値、キーフレームをゆっくり動かすとランダム要素として使い道が多い</v>
       </c>
+      <c r="BO111">
+        <v>5</v>
+      </c>
+      <c r="BP111">
+        <v>5</v>
+      </c>
+      <c r="BQ111" t="str">
+        <v/>
+      </c>
+      <c r="BT111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -21747,6 +23577,18 @@
       <c r="BN112" t="str">
         <v>効果がわかりやすいもの、わかりにくいものが極端　キーフレームはほぼ効果ない</v>
       </c>
+      <c r="BO112">
+        <v>3</v>
+      </c>
+      <c r="BP112">
+        <v>1</v>
+      </c>
+      <c r="BQ112" t="str">
+        <v/>
+      </c>
+      <c r="BT112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -21947,6 +23789,18 @@
       <c r="BN113" t="str">
         <v>効果が極端にかかり揺れが気持ちが悪いことがほとんどなのでまず使わない</v>
       </c>
+      <c r="BO113">
+        <v>0</v>
+      </c>
+      <c r="BP113">
+        <v>0</v>
+      </c>
+      <c r="BQ113" t="str">
+        <v/>
+      </c>
+      <c r="BT113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -22147,6 +24001,18 @@
       <c r="BN114" t="str">
         <v>効果が非常にわかりづらい　まず使わない</v>
       </c>
+      <c r="BO114">
+        <v>0</v>
+      </c>
+      <c r="BP114">
+        <v>0</v>
+      </c>
+      <c r="BQ114" t="str">
+        <v/>
+      </c>
+      <c r="BT114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -22347,6 +24213,18 @@
       <c r="BN115" t="str">
         <v>効果が非常にわかりづらい　まず使わない</v>
       </c>
+      <c r="BO115">
+        <v>0</v>
+      </c>
+      <c r="BP115">
+        <v>0</v>
+      </c>
+      <c r="BQ115" t="str">
+        <v/>
+      </c>
+      <c r="BT115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -22547,6 +24425,18 @@
       <c r="BN116" t="str">
         <v>3D効果としてはあまり機能していない、触るとしたらX軸をゆっくり動かすくらいで使える</v>
       </c>
+      <c r="BO116">
+        <v>1</v>
+      </c>
+      <c r="BP116">
+        <v>0</v>
+      </c>
+      <c r="BQ116" t="str">
+        <v/>
+      </c>
+      <c r="BT116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -22747,6 +24637,18 @@
       <c r="BN117" t="str">
         <v>3D効果としてはあまり機能していない、触るとしたらX軸をゆっくり動かすくらいで使える</v>
       </c>
+      <c r="BO117">
+        <v>1</v>
+      </c>
+      <c r="BP117">
+        <v>0</v>
+      </c>
+      <c r="BQ117" t="str">
+        <v/>
+      </c>
+      <c r="BT117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -22947,6 +24849,18 @@
       <c r="BN118" t="str">
         <v>3D効果としてはあまり機能していない、触るとしたらX軸をゆっくり動かすくらいで使える</v>
       </c>
+      <c r="BO118">
+        <v>1</v>
+      </c>
+      <c r="BP118">
+        <v>0</v>
+      </c>
+      <c r="BQ118" t="str">
+        <v/>
+      </c>
+      <c r="BT118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -23146,6 +25060,6283 @@
       </c>
       <c r="BN119" t="str">
         <v>Scaleと効果がほぼ被るのでまず使わない</v>
+      </c>
+      <c r="BO119">
+        <v>1</v>
+      </c>
+      <c r="BP119">
+        <v>0</v>
+      </c>
+      <c r="BQ119" t="str">
+        <v/>
+      </c>
+      <c r="BT119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B120" t="str">
+        <v>patternMode</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Pattern Mode (0=Radial,1=Sweep,2=Star,3=Arrow,4=Noise,5=Fill,6=Ripple,7=Sparkle)</v>
+      </c>
+      <c r="D120" t="str">
+        <v>-</v>
+      </c>
+      <c r="E120" t="str">
+        <v>-</v>
+      </c>
+      <c r="F120" t="str">
+        <v>-</v>
+      </c>
+      <c r="G120" t="str">
+        <v>-</v>
+      </c>
+      <c r="H120" t="str">
+        <v>-</v>
+      </c>
+      <c r="I120" t="str">
+        <v>-</v>
+      </c>
+      <c r="J120" t="str">
+        <v>-</v>
+      </c>
+      <c r="K120" t="str">
+        <v>-</v>
+      </c>
+      <c r="L120" t="str">
+        <v>-</v>
+      </c>
+      <c r="M120" t="str">
+        <v>-</v>
+      </c>
+      <c r="N120" t="str">
+        <v>-</v>
+      </c>
+      <c r="O120" t="str">
+        <v>-</v>
+      </c>
+      <c r="P120" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q120" t="str">
+        <v>-</v>
+      </c>
+      <c r="R120" t="str">
+        <v>-</v>
+      </c>
+      <c r="S120" t="str">
+        <v>-</v>
+      </c>
+      <c r="T120" t="str">
+        <v>-</v>
+      </c>
+      <c r="U120" t="str">
+        <v>-</v>
+      </c>
+      <c r="V120" t="str">
+        <v>-</v>
+      </c>
+      <c r="W120" t="str">
+        <v>-</v>
+      </c>
+      <c r="X120" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y120" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY120" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO120">
+        <v>5</v>
+      </c>
+      <c r="BP120">
+        <v>0</v>
+      </c>
+      <c r="BQ120" t="str">
+        <v/>
+      </c>
+      <c r="BR120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS120" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT120" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B121" t="str">
+        <v>reverse</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Reverse (0=Expand,1=Converge)</v>
+      </c>
+      <c r="D121" t="str">
+        <v>-</v>
+      </c>
+      <c r="E121" t="str">
+        <v>-</v>
+      </c>
+      <c r="F121" t="str">
+        <v>-</v>
+      </c>
+      <c r="G121" t="str">
+        <v>-</v>
+      </c>
+      <c r="H121" t="str">
+        <v>-</v>
+      </c>
+      <c r="I121" t="str">
+        <v>-</v>
+      </c>
+      <c r="J121" t="str">
+        <v>-</v>
+      </c>
+      <c r="K121" t="str">
+        <v>-</v>
+      </c>
+      <c r="L121" t="str">
+        <v>-</v>
+      </c>
+      <c r="M121" t="str">
+        <v>-</v>
+      </c>
+      <c r="N121" t="str">
+        <v>-</v>
+      </c>
+      <c r="O121" t="str">
+        <v>-</v>
+      </c>
+      <c r="P121" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q121" t="str">
+        <v>-</v>
+      </c>
+      <c r="R121" t="str">
+        <v>-</v>
+      </c>
+      <c r="S121" t="str">
+        <v>-</v>
+      </c>
+      <c r="T121" t="str">
+        <v>-</v>
+      </c>
+      <c r="U121" t="str">
+        <v>-</v>
+      </c>
+      <c r="V121" t="str">
+        <v>-</v>
+      </c>
+      <c r="W121" t="str">
+        <v>-</v>
+      </c>
+      <c r="X121" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y121" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY121" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO121">
+        <v>1</v>
+      </c>
+      <c r="BP121">
+        <v>0</v>
+      </c>
+      <c r="BQ121" t="str">
+        <v/>
+      </c>
+      <c r="BR121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS121" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT121" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B122" t="str">
+        <v>sweepAngle</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Sweep/Arrow/Fill Angle</v>
+      </c>
+      <c r="D122" t="str">
+        <v>-</v>
+      </c>
+      <c r="E122" t="str">
+        <v>-</v>
+      </c>
+      <c r="F122" t="str">
+        <v>-</v>
+      </c>
+      <c r="G122" t="str">
+        <v>-</v>
+      </c>
+      <c r="H122" t="str">
+        <v>-</v>
+      </c>
+      <c r="I122" t="str">
+        <v>-</v>
+      </c>
+      <c r="J122" t="str">
+        <v>-</v>
+      </c>
+      <c r="K122" t="str">
+        <v>-</v>
+      </c>
+      <c r="L122" t="str">
+        <v>-</v>
+      </c>
+      <c r="M122" t="str">
+        <v>-</v>
+      </c>
+      <c r="N122" t="str">
+        <v>-</v>
+      </c>
+      <c r="O122" t="str">
+        <v>-</v>
+      </c>
+      <c r="P122" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q122" t="str">
+        <v>-</v>
+      </c>
+      <c r="R122" t="str">
+        <v>-</v>
+      </c>
+      <c r="S122" t="str">
+        <v>-</v>
+      </c>
+      <c r="T122" t="str">
+        <v>-</v>
+      </c>
+      <c r="U122" t="str">
+        <v>-</v>
+      </c>
+      <c r="V122" t="str">
+        <v>-</v>
+      </c>
+      <c r="W122" t="str">
+        <v>-</v>
+      </c>
+      <c r="X122" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y122" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY122" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO122">
+        <v>1</v>
+      </c>
+      <c r="BP122">
+        <v>0</v>
+      </c>
+      <c r="BQ122" t="str">
+        <v/>
+      </c>
+      <c r="BR122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS122" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT122" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B123" t="str">
+        <v>gridSize</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Grid Size</v>
+      </c>
+      <c r="D123" t="str">
+        <v>-</v>
+      </c>
+      <c r="E123" t="str">
+        <v>-</v>
+      </c>
+      <c r="F123" t="str">
+        <v>-</v>
+      </c>
+      <c r="G123" t="str">
+        <v>-</v>
+      </c>
+      <c r="H123" t="str">
+        <v>-</v>
+      </c>
+      <c r="I123" t="str">
+        <v>-</v>
+      </c>
+      <c r="J123" t="str">
+        <v>-</v>
+      </c>
+      <c r="K123" t="str">
+        <v>-</v>
+      </c>
+      <c r="L123" t="str">
+        <v>-</v>
+      </c>
+      <c r="M123" t="str">
+        <v>-</v>
+      </c>
+      <c r="N123" t="str">
+        <v>-</v>
+      </c>
+      <c r="O123" t="str">
+        <v>-</v>
+      </c>
+      <c r="P123" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q123" t="str">
+        <v>-</v>
+      </c>
+      <c r="R123" t="str">
+        <v>-</v>
+      </c>
+      <c r="S123" t="str">
+        <v>-</v>
+      </c>
+      <c r="T123" t="str">
+        <v>-</v>
+      </c>
+      <c r="U123" t="str">
+        <v>-</v>
+      </c>
+      <c r="V123" t="str">
+        <v>-</v>
+      </c>
+      <c r="W123" t="str">
+        <v>-</v>
+      </c>
+      <c r="X123" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y123" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY123" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO123">
+        <v>5</v>
+      </c>
+      <c r="BP123">
+        <v>1</v>
+      </c>
+      <c r="BQ123" t="str">
+        <v/>
+      </c>
+      <c r="BR123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS123" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT123" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B124" t="str">
+        <v>dotShape</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Dot Shape (0=Square,1=Circle)</v>
+      </c>
+      <c r="D124" t="str">
+        <v>-</v>
+      </c>
+      <c r="E124" t="str">
+        <v>-</v>
+      </c>
+      <c r="F124" t="str">
+        <v>-</v>
+      </c>
+      <c r="G124" t="str">
+        <v>-</v>
+      </c>
+      <c r="H124" t="str">
+        <v>-</v>
+      </c>
+      <c r="I124" t="str">
+        <v>-</v>
+      </c>
+      <c r="J124" t="str">
+        <v>-</v>
+      </c>
+      <c r="K124" t="str">
+        <v>-</v>
+      </c>
+      <c r="L124" t="str">
+        <v>-</v>
+      </c>
+      <c r="M124" t="str">
+        <v>-</v>
+      </c>
+      <c r="N124" t="str">
+        <v>-</v>
+      </c>
+      <c r="O124" t="str">
+        <v>-</v>
+      </c>
+      <c r="P124" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q124" t="str">
+        <v>-</v>
+      </c>
+      <c r="R124" t="str">
+        <v>-</v>
+      </c>
+      <c r="S124" t="str">
+        <v>-</v>
+      </c>
+      <c r="T124" t="str">
+        <v>-</v>
+      </c>
+      <c r="U124" t="str">
+        <v>-</v>
+      </c>
+      <c r="V124" t="str">
+        <v>-</v>
+      </c>
+      <c r="W124" t="str">
+        <v>-</v>
+      </c>
+      <c r="X124" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y124" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY124" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO124">
+        <v>5</v>
+      </c>
+      <c r="BP124">
+        <v>0</v>
+      </c>
+      <c r="BQ124" t="str">
+        <v/>
+      </c>
+      <c r="BR124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS124" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT124" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B125" t="str">
+        <v>edgeJitter</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Edge Roughness</v>
+      </c>
+      <c r="D125" t="str">
+        <v>-</v>
+      </c>
+      <c r="E125" t="str">
+        <v>-</v>
+      </c>
+      <c r="F125" t="str">
+        <v>-</v>
+      </c>
+      <c r="G125" t="str">
+        <v>-</v>
+      </c>
+      <c r="H125" t="str">
+        <v>-</v>
+      </c>
+      <c r="I125" t="str">
+        <v>-</v>
+      </c>
+      <c r="J125" t="str">
+        <v>-</v>
+      </c>
+      <c r="K125" t="str">
+        <v>-</v>
+      </c>
+      <c r="L125" t="str">
+        <v>-</v>
+      </c>
+      <c r="M125" t="str">
+        <v>-</v>
+      </c>
+      <c r="N125" t="str">
+        <v>-</v>
+      </c>
+      <c r="O125" t="str">
+        <v>-</v>
+      </c>
+      <c r="P125" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q125" t="str">
+        <v>-</v>
+      </c>
+      <c r="R125" t="str">
+        <v>-</v>
+      </c>
+      <c r="S125" t="str">
+        <v>-</v>
+      </c>
+      <c r="T125" t="str">
+        <v>-</v>
+      </c>
+      <c r="U125" t="str">
+        <v>-</v>
+      </c>
+      <c r="V125" t="str">
+        <v>-</v>
+      </c>
+      <c r="W125" t="str">
+        <v>-</v>
+      </c>
+      <c r="X125" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y125" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY125" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO125">
+        <v>1</v>
+      </c>
+      <c r="BP125">
+        <v>0</v>
+      </c>
+      <c r="BQ125" t="str">
+        <v/>
+      </c>
+      <c r="BR125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS125" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT125" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B126" t="str">
+        <v>patternSeedX</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Pattern Seed X</v>
+      </c>
+      <c r="D126" t="str">
+        <v>-</v>
+      </c>
+      <c r="E126" t="str">
+        <v>-</v>
+      </c>
+      <c r="F126" t="str">
+        <v>-</v>
+      </c>
+      <c r="G126" t="str">
+        <v>-</v>
+      </c>
+      <c r="H126" t="str">
+        <v>-</v>
+      </c>
+      <c r="I126" t="str">
+        <v>-</v>
+      </c>
+      <c r="J126" t="str">
+        <v>-</v>
+      </c>
+      <c r="K126" t="str">
+        <v>-</v>
+      </c>
+      <c r="L126" t="str">
+        <v>-</v>
+      </c>
+      <c r="M126" t="str">
+        <v>-</v>
+      </c>
+      <c r="N126" t="str">
+        <v>-</v>
+      </c>
+      <c r="O126" t="str">
+        <v>-</v>
+      </c>
+      <c r="P126" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q126" t="str">
+        <v>-</v>
+      </c>
+      <c r="R126" t="str">
+        <v>-</v>
+      </c>
+      <c r="S126" t="str">
+        <v>-</v>
+      </c>
+      <c r="T126" t="str">
+        <v>-</v>
+      </c>
+      <c r="U126" t="str">
+        <v>-</v>
+      </c>
+      <c r="V126" t="str">
+        <v>-</v>
+      </c>
+      <c r="W126" t="str">
+        <v>-</v>
+      </c>
+      <c r="X126" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y126" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY126" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO126">
+        <v>3</v>
+      </c>
+      <c r="BP126">
+        <v>0</v>
+      </c>
+      <c r="BQ126" t="str">
+        <v/>
+      </c>
+      <c r="BR126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS126" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT126" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B127" t="str">
+        <v>patternSeedY</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Pattern Seed Y</v>
+      </c>
+      <c r="D127" t="str">
+        <v>-</v>
+      </c>
+      <c r="E127" t="str">
+        <v>-</v>
+      </c>
+      <c r="F127" t="str">
+        <v>-</v>
+      </c>
+      <c r="G127" t="str">
+        <v>-</v>
+      </c>
+      <c r="H127" t="str">
+        <v>-</v>
+      </c>
+      <c r="I127" t="str">
+        <v>-</v>
+      </c>
+      <c r="J127" t="str">
+        <v>-</v>
+      </c>
+      <c r="K127" t="str">
+        <v>-</v>
+      </c>
+      <c r="L127" t="str">
+        <v>-</v>
+      </c>
+      <c r="M127" t="str">
+        <v>-</v>
+      </c>
+      <c r="N127" t="str">
+        <v>-</v>
+      </c>
+      <c r="O127" t="str">
+        <v>-</v>
+      </c>
+      <c r="P127" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q127" t="str">
+        <v>-</v>
+      </c>
+      <c r="R127" t="str">
+        <v>-</v>
+      </c>
+      <c r="S127" t="str">
+        <v>-</v>
+      </c>
+      <c r="T127" t="str">
+        <v>-</v>
+      </c>
+      <c r="U127" t="str">
+        <v>-</v>
+      </c>
+      <c r="V127" t="str">
+        <v>-</v>
+      </c>
+      <c r="W127" t="str">
+        <v>-</v>
+      </c>
+      <c r="X127" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y127" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY127" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO127">
+        <v>3</v>
+      </c>
+      <c r="BP127">
+        <v>0</v>
+      </c>
+      <c r="BQ127" t="str">
+        <v/>
+      </c>
+      <c r="BR127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS127" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT127" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B128" t="str">
+        <v>threshold</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Noise Density Threshold</v>
+      </c>
+      <c r="D128" t="str">
+        <v>-</v>
+      </c>
+      <c r="E128" t="str">
+        <v>-</v>
+      </c>
+      <c r="F128" t="str">
+        <v>-</v>
+      </c>
+      <c r="G128" t="str">
+        <v>-</v>
+      </c>
+      <c r="H128" t="str">
+        <v>-</v>
+      </c>
+      <c r="I128" t="str">
+        <v>-</v>
+      </c>
+      <c r="J128" t="str">
+        <v>-</v>
+      </c>
+      <c r="K128" t="str">
+        <v>-</v>
+      </c>
+      <c r="L128" t="str">
+        <v>-</v>
+      </c>
+      <c r="M128" t="str">
+        <v>-</v>
+      </c>
+      <c r="N128" t="str">
+        <v>-</v>
+      </c>
+      <c r="O128" t="str">
+        <v>-</v>
+      </c>
+      <c r="P128" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q128" t="str">
+        <v>-</v>
+      </c>
+      <c r="R128" t="str">
+        <v>-</v>
+      </c>
+      <c r="S128" t="str">
+        <v>-</v>
+      </c>
+      <c r="T128" t="str">
+        <v>-</v>
+      </c>
+      <c r="U128" t="str">
+        <v>-</v>
+      </c>
+      <c r="V128" t="str">
+        <v>-</v>
+      </c>
+      <c r="W128" t="str">
+        <v>-</v>
+      </c>
+      <c r="X128" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y128" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY128" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO128">
+        <v>2</v>
+      </c>
+      <c r="BP128">
+        <v>0</v>
+      </c>
+      <c r="BQ128" t="str">
+        <v/>
+      </c>
+      <c r="BR128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS128" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT128" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B129" t="str">
+        <v>fillAmount</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Dot Fill %</v>
+      </c>
+      <c r="D129" t="str">
+        <v>-</v>
+      </c>
+      <c r="E129" t="str">
+        <v>-</v>
+      </c>
+      <c r="F129" t="str">
+        <v>-</v>
+      </c>
+      <c r="G129" t="str">
+        <v>-</v>
+      </c>
+      <c r="H129" t="str">
+        <v>-</v>
+      </c>
+      <c r="I129" t="str">
+        <v>-</v>
+      </c>
+      <c r="J129" t="str">
+        <v>-</v>
+      </c>
+      <c r="K129" t="str">
+        <v>-</v>
+      </c>
+      <c r="L129" t="str">
+        <v>-</v>
+      </c>
+      <c r="M129" t="str">
+        <v>-</v>
+      </c>
+      <c r="N129" t="str">
+        <v>-</v>
+      </c>
+      <c r="O129" t="str">
+        <v>-</v>
+      </c>
+      <c r="P129" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q129" t="str">
+        <v>-</v>
+      </c>
+      <c r="R129" t="str">
+        <v>-</v>
+      </c>
+      <c r="S129" t="str">
+        <v>-</v>
+      </c>
+      <c r="T129" t="str">
+        <v>-</v>
+      </c>
+      <c r="U129" t="str">
+        <v>-</v>
+      </c>
+      <c r="V129" t="str">
+        <v>-</v>
+      </c>
+      <c r="W129" t="str">
+        <v>-</v>
+      </c>
+      <c r="X129" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y129" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY129" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO129">
+        <v>5</v>
+      </c>
+      <c r="BP129">
+        <v>3</v>
+      </c>
+      <c r="BQ129" t="str">
+        <v/>
+      </c>
+      <c r="BR129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS129" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT129" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B130" t="str">
+        <v>colorMode</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Color Mode (0=Single,1=Famicom Palette)</v>
+      </c>
+      <c r="D130" t="str">
+        <v>-</v>
+      </c>
+      <c r="E130" t="str">
+        <v>-</v>
+      </c>
+      <c r="F130" t="str">
+        <v>-</v>
+      </c>
+      <c r="G130" t="str">
+        <v>-</v>
+      </c>
+      <c r="H130" t="str">
+        <v>-</v>
+      </c>
+      <c r="I130" t="str">
+        <v>-</v>
+      </c>
+      <c r="J130" t="str">
+        <v>-</v>
+      </c>
+      <c r="K130" t="str">
+        <v>-</v>
+      </c>
+      <c r="L130" t="str">
+        <v>-</v>
+      </c>
+      <c r="M130" t="str">
+        <v>-</v>
+      </c>
+      <c r="N130" t="str">
+        <v>-</v>
+      </c>
+      <c r="O130" t="str">
+        <v>-</v>
+      </c>
+      <c r="P130" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q130" t="str">
+        <v>-</v>
+      </c>
+      <c r="R130" t="str">
+        <v>-</v>
+      </c>
+      <c r="S130" t="str">
+        <v>-</v>
+      </c>
+      <c r="T130" t="str">
+        <v>-</v>
+      </c>
+      <c r="U130" t="str">
+        <v>-</v>
+      </c>
+      <c r="V130" t="str">
+        <v>-</v>
+      </c>
+      <c r="W130" t="str">
+        <v>-</v>
+      </c>
+      <c r="X130" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y130" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY130" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO130">
+        <v>1</v>
+      </c>
+      <c r="BP130">
+        <v>0</v>
+      </c>
+      <c r="BQ130" t="str">
+        <v/>
+      </c>
+      <c r="BR130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS130" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT130" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B131" t="str">
+        <v>streakWidth</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Streak Width</v>
+      </c>
+      <c r="D131" t="str">
+        <v>-</v>
+      </c>
+      <c r="E131" t="str">
+        <v>-</v>
+      </c>
+      <c r="F131" t="str">
+        <v>-</v>
+      </c>
+      <c r="G131" t="str">
+        <v>-</v>
+      </c>
+      <c r="H131" t="str">
+        <v>-</v>
+      </c>
+      <c r="I131" t="str">
+        <v>-</v>
+      </c>
+      <c r="J131" t="str">
+        <v>-</v>
+      </c>
+      <c r="K131" t="str">
+        <v>-</v>
+      </c>
+      <c r="L131" t="str">
+        <v>-</v>
+      </c>
+      <c r="M131" t="str">
+        <v>-</v>
+      </c>
+      <c r="N131" t="str">
+        <v>-</v>
+      </c>
+      <c r="O131" t="str">
+        <v>-</v>
+      </c>
+      <c r="P131" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q131" t="str">
+        <v>-</v>
+      </c>
+      <c r="R131" t="str">
+        <v>-</v>
+      </c>
+      <c r="S131" t="str">
+        <v>-</v>
+      </c>
+      <c r="T131" t="str">
+        <v>-</v>
+      </c>
+      <c r="U131" t="str">
+        <v>-</v>
+      </c>
+      <c r="V131" t="str">
+        <v>-</v>
+      </c>
+      <c r="W131" t="str">
+        <v>-</v>
+      </c>
+      <c r="X131" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y131" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY131" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ131" t="str">
+        <v>-</v>
+      </c>
+      <c r="BR131">
+        <v>5</v>
+      </c>
+      <c r="BS131">
+        <v>5</v>
+      </c>
+      <c r="BT131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B132" t="str">
+        <v>taper</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Edge Taper %</v>
+      </c>
+      <c r="D132" t="str">
+        <v>-</v>
+      </c>
+      <c r="E132" t="str">
+        <v>-</v>
+      </c>
+      <c r="F132" t="str">
+        <v>-</v>
+      </c>
+      <c r="G132" t="str">
+        <v>-</v>
+      </c>
+      <c r="H132" t="str">
+        <v>-</v>
+      </c>
+      <c r="I132" t="str">
+        <v>-</v>
+      </c>
+      <c r="J132" t="str">
+        <v>-</v>
+      </c>
+      <c r="K132" t="str">
+        <v>-</v>
+      </c>
+      <c r="L132" t="str">
+        <v>-</v>
+      </c>
+      <c r="M132" t="str">
+        <v>-</v>
+      </c>
+      <c r="N132" t="str">
+        <v>-</v>
+      </c>
+      <c r="O132" t="str">
+        <v>-</v>
+      </c>
+      <c r="P132" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q132" t="str">
+        <v>-</v>
+      </c>
+      <c r="R132" t="str">
+        <v>-</v>
+      </c>
+      <c r="S132" t="str">
+        <v>-</v>
+      </c>
+      <c r="T132" t="str">
+        <v>-</v>
+      </c>
+      <c r="U132" t="str">
+        <v>-</v>
+      </c>
+      <c r="V132" t="str">
+        <v>-</v>
+      </c>
+      <c r="W132" t="str">
+        <v>-</v>
+      </c>
+      <c r="X132" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y132" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY132" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ132" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS132">
+        <v>0</v>
+      </c>
+      <c r="BT132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B133" t="str">
+        <v>softness</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Streak Softness</v>
+      </c>
+      <c r="D133" t="str">
+        <v>-</v>
+      </c>
+      <c r="E133" t="str">
+        <v>-</v>
+      </c>
+      <c r="F133" t="str">
+        <v>-</v>
+      </c>
+      <c r="G133" t="str">
+        <v>-</v>
+      </c>
+      <c r="H133" t="str">
+        <v>-</v>
+      </c>
+      <c r="I133" t="str">
+        <v>-</v>
+      </c>
+      <c r="J133" t="str">
+        <v>-</v>
+      </c>
+      <c r="K133" t="str">
+        <v>-</v>
+      </c>
+      <c r="L133" t="str">
+        <v>-</v>
+      </c>
+      <c r="M133" t="str">
+        <v>-</v>
+      </c>
+      <c r="N133" t="str">
+        <v>-</v>
+      </c>
+      <c r="O133" t="str">
+        <v>-</v>
+      </c>
+      <c r="P133" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q133" t="str">
+        <v>-</v>
+      </c>
+      <c r="R133" t="str">
+        <v>-</v>
+      </c>
+      <c r="S133" t="str">
+        <v>-</v>
+      </c>
+      <c r="T133" t="str">
+        <v>-</v>
+      </c>
+      <c r="U133" t="str">
+        <v>-</v>
+      </c>
+      <c r="V133" t="str">
+        <v>-</v>
+      </c>
+      <c r="W133" t="str">
+        <v>-</v>
+      </c>
+      <c r="X133" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y133" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY133" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ133" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS133">
+        <v>0</v>
+      </c>
+      <c r="BT133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B134" t="str">
+        <v>perspective</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Perspective Depth %</v>
+      </c>
+      <c r="D134" t="str">
+        <v>-</v>
+      </c>
+      <c r="E134" t="str">
+        <v>-</v>
+      </c>
+      <c r="F134" t="str">
+        <v>-</v>
+      </c>
+      <c r="G134" t="str">
+        <v>-</v>
+      </c>
+      <c r="H134" t="str">
+        <v>-</v>
+      </c>
+      <c r="I134" t="str">
+        <v>-</v>
+      </c>
+      <c r="J134" t="str">
+        <v>-</v>
+      </c>
+      <c r="K134" t="str">
+        <v>-</v>
+      </c>
+      <c r="L134" t="str">
+        <v>-</v>
+      </c>
+      <c r="M134" t="str">
+        <v>-</v>
+      </c>
+      <c r="N134" t="str">
+        <v>-</v>
+      </c>
+      <c r="O134" t="str">
+        <v>-</v>
+      </c>
+      <c r="P134" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q134" t="str">
+        <v>-</v>
+      </c>
+      <c r="R134" t="str">
+        <v>-</v>
+      </c>
+      <c r="S134" t="str">
+        <v>-</v>
+      </c>
+      <c r="T134" t="str">
+        <v>-</v>
+      </c>
+      <c r="U134" t="str">
+        <v>-</v>
+      </c>
+      <c r="V134" t="str">
+        <v>-</v>
+      </c>
+      <c r="W134" t="str">
+        <v>-</v>
+      </c>
+      <c r="X134" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y134" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY134" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ134" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS134">
+        <v>0</v>
+      </c>
+      <c r="BT134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B135" t="str">
+        <v>perspectiveFlip</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Perspective Flip (0/1)</v>
+      </c>
+      <c r="D135" t="str">
+        <v>-</v>
+      </c>
+      <c r="E135" t="str">
+        <v>-</v>
+      </c>
+      <c r="F135" t="str">
+        <v>-</v>
+      </c>
+      <c r="G135" t="str">
+        <v>-</v>
+      </c>
+      <c r="H135" t="str">
+        <v>-</v>
+      </c>
+      <c r="I135" t="str">
+        <v>-</v>
+      </c>
+      <c r="J135" t="str">
+        <v>-</v>
+      </c>
+      <c r="K135" t="str">
+        <v>-</v>
+      </c>
+      <c r="L135" t="str">
+        <v>-</v>
+      </c>
+      <c r="M135" t="str">
+        <v>-</v>
+      </c>
+      <c r="N135" t="str">
+        <v>-</v>
+      </c>
+      <c r="O135" t="str">
+        <v>-</v>
+      </c>
+      <c r="P135" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q135" t="str">
+        <v>-</v>
+      </c>
+      <c r="R135" t="str">
+        <v>-</v>
+      </c>
+      <c r="S135" t="str">
+        <v>-</v>
+      </c>
+      <c r="T135" t="str">
+        <v>-</v>
+      </c>
+      <c r="U135" t="str">
+        <v>-</v>
+      </c>
+      <c r="V135" t="str">
+        <v>-</v>
+      </c>
+      <c r="W135" t="str">
+        <v>-</v>
+      </c>
+      <c r="X135" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y135" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY135" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ135" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS135">
+        <v>0</v>
+      </c>
+      <c r="BT135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B136" t="str">
+        <v>waveAmplitude</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Wave Amplitude</v>
+      </c>
+      <c r="D136" t="str">
+        <v>-</v>
+      </c>
+      <c r="E136" t="str">
+        <v>-</v>
+      </c>
+      <c r="F136" t="str">
+        <v>-</v>
+      </c>
+      <c r="G136" t="str">
+        <v>-</v>
+      </c>
+      <c r="H136" t="str">
+        <v>-</v>
+      </c>
+      <c r="I136" t="str">
+        <v>-</v>
+      </c>
+      <c r="J136" t="str">
+        <v>-</v>
+      </c>
+      <c r="K136" t="str">
+        <v>-</v>
+      </c>
+      <c r="L136" t="str">
+        <v>-</v>
+      </c>
+      <c r="M136" t="str">
+        <v>-</v>
+      </c>
+      <c r="N136" t="str">
+        <v>-</v>
+      </c>
+      <c r="O136" t="str">
+        <v>-</v>
+      </c>
+      <c r="P136" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q136" t="str">
+        <v>-</v>
+      </c>
+      <c r="R136" t="str">
+        <v>-</v>
+      </c>
+      <c r="S136" t="str">
+        <v>-</v>
+      </c>
+      <c r="T136" t="str">
+        <v>-</v>
+      </c>
+      <c r="U136" t="str">
+        <v>-</v>
+      </c>
+      <c r="V136" t="str">
+        <v>-</v>
+      </c>
+      <c r="W136" t="str">
+        <v>-</v>
+      </c>
+      <c r="X136" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y136" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY136" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ136" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS136">
+        <v>0</v>
+      </c>
+      <c r="BT136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B137" t="str">
+        <v>waveSpeed</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Wave Speed</v>
+      </c>
+      <c r="D137" t="str">
+        <v>-</v>
+      </c>
+      <c r="E137" t="str">
+        <v>-</v>
+      </c>
+      <c r="F137" t="str">
+        <v>-</v>
+      </c>
+      <c r="G137" t="str">
+        <v>-</v>
+      </c>
+      <c r="H137" t="str">
+        <v>-</v>
+      </c>
+      <c r="I137" t="str">
+        <v>-</v>
+      </c>
+      <c r="J137" t="str">
+        <v>-</v>
+      </c>
+      <c r="K137" t="str">
+        <v>-</v>
+      </c>
+      <c r="L137" t="str">
+        <v>-</v>
+      </c>
+      <c r="M137" t="str">
+        <v>-</v>
+      </c>
+      <c r="N137" t="str">
+        <v>-</v>
+      </c>
+      <c r="O137" t="str">
+        <v>-</v>
+      </c>
+      <c r="P137" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q137" t="str">
+        <v>-</v>
+      </c>
+      <c r="R137" t="str">
+        <v>-</v>
+      </c>
+      <c r="S137" t="str">
+        <v>-</v>
+      </c>
+      <c r="T137" t="str">
+        <v>-</v>
+      </c>
+      <c r="U137" t="str">
+        <v>-</v>
+      </c>
+      <c r="V137" t="str">
+        <v>-</v>
+      </c>
+      <c r="W137" t="str">
+        <v>-</v>
+      </c>
+      <c r="X137" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y137" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY137" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ137" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS137">
+        <v>0</v>
+      </c>
+      <c r="BT137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B138" t="str">
+        <v>bgStarCount</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Background Star Count</v>
+      </c>
+      <c r="D138" t="str">
+        <v>-</v>
+      </c>
+      <c r="E138" t="str">
+        <v>-</v>
+      </c>
+      <c r="F138" t="str">
+        <v>-</v>
+      </c>
+      <c r="G138" t="str">
+        <v>-</v>
+      </c>
+      <c r="H138" t="str">
+        <v>-</v>
+      </c>
+      <c r="I138" t="str">
+        <v>-</v>
+      </c>
+      <c r="J138" t="str">
+        <v>-</v>
+      </c>
+      <c r="K138" t="str">
+        <v>-</v>
+      </c>
+      <c r="L138" t="str">
+        <v>-</v>
+      </c>
+      <c r="M138" t="str">
+        <v>-</v>
+      </c>
+      <c r="N138" t="str">
+        <v>-</v>
+      </c>
+      <c r="O138" t="str">
+        <v>-</v>
+      </c>
+      <c r="P138" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q138" t="str">
+        <v>-</v>
+      </c>
+      <c r="R138" t="str">
+        <v>-</v>
+      </c>
+      <c r="S138" t="str">
+        <v>-</v>
+      </c>
+      <c r="T138" t="str">
+        <v>-</v>
+      </c>
+      <c r="U138" t="str">
+        <v>-</v>
+      </c>
+      <c r="V138" t="str">
+        <v>-</v>
+      </c>
+      <c r="W138" t="str">
+        <v>-</v>
+      </c>
+      <c r="X138" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y138" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY138" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ138" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS138">
+        <v>0</v>
+      </c>
+      <c r="BT138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B139" t="str">
+        <v>bgStarSize</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Background Star Size</v>
+      </c>
+      <c r="D139" t="str">
+        <v>-</v>
+      </c>
+      <c r="E139" t="str">
+        <v>-</v>
+      </c>
+      <c r="F139" t="str">
+        <v>-</v>
+      </c>
+      <c r="G139" t="str">
+        <v>-</v>
+      </c>
+      <c r="H139" t="str">
+        <v>-</v>
+      </c>
+      <c r="I139" t="str">
+        <v>-</v>
+      </c>
+      <c r="J139" t="str">
+        <v>-</v>
+      </c>
+      <c r="K139" t="str">
+        <v>-</v>
+      </c>
+      <c r="L139" t="str">
+        <v>-</v>
+      </c>
+      <c r="M139" t="str">
+        <v>-</v>
+      </c>
+      <c r="N139" t="str">
+        <v>-</v>
+      </c>
+      <c r="O139" t="str">
+        <v>-</v>
+      </c>
+      <c r="P139" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q139" t="str">
+        <v>-</v>
+      </c>
+      <c r="R139" t="str">
+        <v>-</v>
+      </c>
+      <c r="S139" t="str">
+        <v>-</v>
+      </c>
+      <c r="T139" t="str">
+        <v>-</v>
+      </c>
+      <c r="U139" t="str">
+        <v>-</v>
+      </c>
+      <c r="V139" t="str">
+        <v>-</v>
+      </c>
+      <c r="W139" t="str">
+        <v>-</v>
+      </c>
+      <c r="X139" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y139" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY139" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ139" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS139">
+        <v>0</v>
+      </c>
+      <c r="BT139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B140" t="str">
+        <v>glintCount</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Band Star Count</v>
+      </c>
+      <c r="D140" t="str">
+        <v>-</v>
+      </c>
+      <c r="E140" t="str">
+        <v>-</v>
+      </c>
+      <c r="F140" t="str">
+        <v>-</v>
+      </c>
+      <c r="G140" t="str">
+        <v>-</v>
+      </c>
+      <c r="H140" t="str">
+        <v>-</v>
+      </c>
+      <c r="I140" t="str">
+        <v>-</v>
+      </c>
+      <c r="J140" t="str">
+        <v>-</v>
+      </c>
+      <c r="K140" t="str">
+        <v>-</v>
+      </c>
+      <c r="L140" t="str">
+        <v>-</v>
+      </c>
+      <c r="M140" t="str">
+        <v>-</v>
+      </c>
+      <c r="N140" t="str">
+        <v>-</v>
+      </c>
+      <c r="O140" t="str">
+        <v>-</v>
+      </c>
+      <c r="P140" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q140" t="str">
+        <v>-</v>
+      </c>
+      <c r="R140" t="str">
+        <v>-</v>
+      </c>
+      <c r="S140" t="str">
+        <v>-</v>
+      </c>
+      <c r="T140" t="str">
+        <v>-</v>
+      </c>
+      <c r="U140" t="str">
+        <v>-</v>
+      </c>
+      <c r="V140" t="str">
+        <v>-</v>
+      </c>
+      <c r="W140" t="str">
+        <v>-</v>
+      </c>
+      <c r="X140" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y140" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY140" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ140" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS140">
+        <v>0</v>
+      </c>
+      <c r="BT140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B141" t="str">
+        <v>glintSpread</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Band Star Spread %</v>
+      </c>
+      <c r="D141" t="str">
+        <v>-</v>
+      </c>
+      <c r="E141" t="str">
+        <v>-</v>
+      </c>
+      <c r="F141" t="str">
+        <v>-</v>
+      </c>
+      <c r="G141" t="str">
+        <v>-</v>
+      </c>
+      <c r="H141" t="str">
+        <v>-</v>
+      </c>
+      <c r="I141" t="str">
+        <v>-</v>
+      </c>
+      <c r="J141" t="str">
+        <v>-</v>
+      </c>
+      <c r="K141" t="str">
+        <v>-</v>
+      </c>
+      <c r="L141" t="str">
+        <v>-</v>
+      </c>
+      <c r="M141" t="str">
+        <v>-</v>
+      </c>
+      <c r="N141" t="str">
+        <v>-</v>
+      </c>
+      <c r="O141" t="str">
+        <v>-</v>
+      </c>
+      <c r="P141" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q141" t="str">
+        <v>-</v>
+      </c>
+      <c r="R141" t="str">
+        <v>-</v>
+      </c>
+      <c r="S141" t="str">
+        <v>-</v>
+      </c>
+      <c r="T141" t="str">
+        <v>-</v>
+      </c>
+      <c r="U141" t="str">
+        <v>-</v>
+      </c>
+      <c r="V141" t="str">
+        <v>-</v>
+      </c>
+      <c r="W141" t="str">
+        <v>-</v>
+      </c>
+      <c r="X141" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y141" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY141" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ141" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS141">
+        <v>0</v>
+      </c>
+      <c r="BT141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B142" t="str">
+        <v>glintSize</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Band Star Size</v>
+      </c>
+      <c r="D142" t="str">
+        <v>-</v>
+      </c>
+      <c r="E142" t="str">
+        <v>-</v>
+      </c>
+      <c r="F142" t="str">
+        <v>-</v>
+      </c>
+      <c r="G142" t="str">
+        <v>-</v>
+      </c>
+      <c r="H142" t="str">
+        <v>-</v>
+      </c>
+      <c r="I142" t="str">
+        <v>-</v>
+      </c>
+      <c r="J142" t="str">
+        <v>-</v>
+      </c>
+      <c r="K142" t="str">
+        <v>-</v>
+      </c>
+      <c r="L142" t="str">
+        <v>-</v>
+      </c>
+      <c r="M142" t="str">
+        <v>-</v>
+      </c>
+      <c r="N142" t="str">
+        <v>-</v>
+      </c>
+      <c r="O142" t="str">
+        <v>-</v>
+      </c>
+      <c r="P142" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q142" t="str">
+        <v>-</v>
+      </c>
+      <c r="R142" t="str">
+        <v>-</v>
+      </c>
+      <c r="S142" t="str">
+        <v>-</v>
+      </c>
+      <c r="T142" t="str">
+        <v>-</v>
+      </c>
+      <c r="U142" t="str">
+        <v>-</v>
+      </c>
+      <c r="V142" t="str">
+        <v>-</v>
+      </c>
+      <c r="W142" t="str">
+        <v>-</v>
+      </c>
+      <c r="X142" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y142" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY142" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ142" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS142">
+        <v>0</v>
+      </c>
+      <c r="BT142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B143" t="str">
+        <v>sparkleChance</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Bright Flare Chance %</v>
+      </c>
+      <c r="D143" t="str">
+        <v>-</v>
+      </c>
+      <c r="E143" t="str">
+        <v>-</v>
+      </c>
+      <c r="F143" t="str">
+        <v>-</v>
+      </c>
+      <c r="G143" t="str">
+        <v>-</v>
+      </c>
+      <c r="H143" t="str">
+        <v>-</v>
+      </c>
+      <c r="I143" t="str">
+        <v>-</v>
+      </c>
+      <c r="J143" t="str">
+        <v>-</v>
+      </c>
+      <c r="K143" t="str">
+        <v>-</v>
+      </c>
+      <c r="L143" t="str">
+        <v>-</v>
+      </c>
+      <c r="M143" t="str">
+        <v>-</v>
+      </c>
+      <c r="N143" t="str">
+        <v>-</v>
+      </c>
+      <c r="O143" t="str">
+        <v>-</v>
+      </c>
+      <c r="P143" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q143" t="str">
+        <v>-</v>
+      </c>
+      <c r="R143" t="str">
+        <v>-</v>
+      </c>
+      <c r="S143" t="str">
+        <v>-</v>
+      </c>
+      <c r="T143" t="str">
+        <v>-</v>
+      </c>
+      <c r="U143" t="str">
+        <v>-</v>
+      </c>
+      <c r="V143" t="str">
+        <v>-</v>
+      </c>
+      <c r="W143" t="str">
+        <v>-</v>
+      </c>
+      <c r="X143" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y143" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY143" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ143" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS143">
+        <v>0</v>
+      </c>
+      <c r="BT143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B144" t="str">
+        <v>scatterRate</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Spill Frequency</v>
+      </c>
+      <c r="D144" t="str">
+        <v>-</v>
+      </c>
+      <c r="E144" t="str">
+        <v>-</v>
+      </c>
+      <c r="F144" t="str">
+        <v>-</v>
+      </c>
+      <c r="G144" t="str">
+        <v>-</v>
+      </c>
+      <c r="H144" t="str">
+        <v>-</v>
+      </c>
+      <c r="I144" t="str">
+        <v>-</v>
+      </c>
+      <c r="J144" t="str">
+        <v>-</v>
+      </c>
+      <c r="K144" t="str">
+        <v>-</v>
+      </c>
+      <c r="L144" t="str">
+        <v>-</v>
+      </c>
+      <c r="M144" t="str">
+        <v>-</v>
+      </c>
+      <c r="N144" t="str">
+        <v>-</v>
+      </c>
+      <c r="O144" t="str">
+        <v>-</v>
+      </c>
+      <c r="P144" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q144" t="str">
+        <v>-</v>
+      </c>
+      <c r="R144" t="str">
+        <v>-</v>
+      </c>
+      <c r="S144" t="str">
+        <v>-</v>
+      </c>
+      <c r="T144" t="str">
+        <v>-</v>
+      </c>
+      <c r="U144" t="str">
+        <v>-</v>
+      </c>
+      <c r="V144" t="str">
+        <v>-</v>
+      </c>
+      <c r="W144" t="str">
+        <v>-</v>
+      </c>
+      <c r="X144" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y144" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY144" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ144" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS144">
+        <v>0</v>
+      </c>
+      <c r="BT144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B145" t="str">
+        <v>scatterSpeed</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Spill Fall Speed</v>
+      </c>
+      <c r="D145" t="str">
+        <v>-</v>
+      </c>
+      <c r="E145" t="str">
+        <v>-</v>
+      </c>
+      <c r="F145" t="str">
+        <v>-</v>
+      </c>
+      <c r="G145" t="str">
+        <v>-</v>
+      </c>
+      <c r="H145" t="str">
+        <v>-</v>
+      </c>
+      <c r="I145" t="str">
+        <v>-</v>
+      </c>
+      <c r="J145" t="str">
+        <v>-</v>
+      </c>
+      <c r="K145" t="str">
+        <v>-</v>
+      </c>
+      <c r="L145" t="str">
+        <v>-</v>
+      </c>
+      <c r="M145" t="str">
+        <v>-</v>
+      </c>
+      <c r="N145" t="str">
+        <v>-</v>
+      </c>
+      <c r="O145" t="str">
+        <v>-</v>
+      </c>
+      <c r="P145" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q145" t="str">
+        <v>-</v>
+      </c>
+      <c r="R145" t="str">
+        <v>-</v>
+      </c>
+      <c r="S145" t="str">
+        <v>-</v>
+      </c>
+      <c r="T145" t="str">
+        <v>-</v>
+      </c>
+      <c r="U145" t="str">
+        <v>-</v>
+      </c>
+      <c r="V145" t="str">
+        <v>-</v>
+      </c>
+      <c r="W145" t="str">
+        <v>-</v>
+      </c>
+      <c r="X145" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y145" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY145" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ145" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS145">
+        <v>0</v>
+      </c>
+      <c r="BT145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B146" t="str">
+        <v>scatterLifetime</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Spill Lifetime</v>
+      </c>
+      <c r="D146" t="str">
+        <v>-</v>
+      </c>
+      <c r="E146" t="str">
+        <v>-</v>
+      </c>
+      <c r="F146" t="str">
+        <v>-</v>
+      </c>
+      <c r="G146" t="str">
+        <v>-</v>
+      </c>
+      <c r="H146" t="str">
+        <v>-</v>
+      </c>
+      <c r="I146" t="str">
+        <v>-</v>
+      </c>
+      <c r="J146" t="str">
+        <v>-</v>
+      </c>
+      <c r="K146" t="str">
+        <v>-</v>
+      </c>
+      <c r="L146" t="str">
+        <v>-</v>
+      </c>
+      <c r="M146" t="str">
+        <v>-</v>
+      </c>
+      <c r="N146" t="str">
+        <v>-</v>
+      </c>
+      <c r="O146" t="str">
+        <v>-</v>
+      </c>
+      <c r="P146" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q146" t="str">
+        <v>-</v>
+      </c>
+      <c r="R146" t="str">
+        <v>-</v>
+      </c>
+      <c r="S146" t="str">
+        <v>-</v>
+      </c>
+      <c r="T146" t="str">
+        <v>-</v>
+      </c>
+      <c r="U146" t="str">
+        <v>-</v>
+      </c>
+      <c r="V146" t="str">
+        <v>-</v>
+      </c>
+      <c r="W146" t="str">
+        <v>-</v>
+      </c>
+      <c r="X146" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y146" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY146" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ146" t="str">
+        <v>-</v>
+      </c>
+      <c r="BS146">
+        <v>0</v>
+      </c>
+      <c r="BT146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B147" t="str">
+        <v>scatterSize</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Spill Particle Size</v>
+      </c>
+      <c r="D147" t="str">
+        <v>-</v>
+      </c>
+      <c r="E147" t="str">
+        <v>-</v>
+      </c>
+      <c r="F147" t="str">
+        <v>-</v>
+      </c>
+      <c r="G147" t="str">
+        <v>-</v>
+      </c>
+      <c r="H147" t="str">
+        <v>-</v>
+      </c>
+      <c r="I147" t="str">
+        <v>-</v>
+      </c>
+      <c r="J147" t="str">
+        <v>-</v>
+      </c>
+      <c r="K147" t="str">
+        <v>-</v>
+      </c>
+      <c r="L147" t="str">
+        <v>-</v>
+      </c>
+      <c r="M147" t="str">
+        <v>-</v>
+      </c>
+      <c r="N147" t="str">
+        <v>-</v>
+      </c>
+      <c r="O147" t="str">
+        <v>-</v>
+      </c>
+      <c r="P147" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q147" t="str">
+        <v>-</v>
+      </c>
+      <c r="R147" t="str">
+        <v>-</v>
+      </c>
+      <c r="S147" t="str">
+        <v>-</v>
+      </c>
+      <c r="T147" t="str">
+        <v>-</v>
+      </c>
+      <c r="U147" t="str">
+        <v>-</v>
+      </c>
+      <c r="V147" t="str">
+        <v>-</v>
+      </c>
+      <c r="W147" t="str">
+        <v>-</v>
+      </c>
+      <c r="X147" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y147" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY147" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ147" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="B148" t="str">
+        <v>scatterShapeType</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Spill Shape (0-11)</v>
+      </c>
+      <c r="D148" t="str">
+        <v>-</v>
+      </c>
+      <c r="E148" t="str">
+        <v>-</v>
+      </c>
+      <c r="F148" t="str">
+        <v>-</v>
+      </c>
+      <c r="G148" t="str">
+        <v>-</v>
+      </c>
+      <c r="H148" t="str">
+        <v>-</v>
+      </c>
+      <c r="I148" t="str">
+        <v>-</v>
+      </c>
+      <c r="J148" t="str">
+        <v>-</v>
+      </c>
+      <c r="K148" t="str">
+        <v>-</v>
+      </c>
+      <c r="L148" t="str">
+        <v>-</v>
+      </c>
+      <c r="M148" t="str">
+        <v>-</v>
+      </c>
+      <c r="N148" t="str">
+        <v>-</v>
+      </c>
+      <c r="O148" t="str">
+        <v>-</v>
+      </c>
+      <c r="P148" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q148" t="str">
+        <v>-</v>
+      </c>
+      <c r="R148" t="str">
+        <v>-</v>
+      </c>
+      <c r="S148" t="str">
+        <v>-</v>
+      </c>
+      <c r="T148" t="str">
+        <v>-</v>
+      </c>
+      <c r="U148" t="str">
+        <v>-</v>
+      </c>
+      <c r="V148" t="str">
+        <v>-</v>
+      </c>
+      <c r="W148" t="str">
+        <v>-</v>
+      </c>
+      <c r="X148" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y148" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AB148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AC148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AD148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AE148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AF148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AG148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AH148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AI148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AJ148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AK148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AL148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AM148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AN148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AO148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AP148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AQ148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AR148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AS148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AT148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AU148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AV148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AW148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AX148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AY148" t="str">
+        <v>-</v>
+      </c>
+      <c r="AZ148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BA148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BB148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BC148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BD148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BE148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BF148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BG148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BH148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BI148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BJ148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BK148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BL148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BM148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BN148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BO148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BP148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BQ148" t="str">
+        <v>-</v>
+      </c>
+      <c r="BT148" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -23178,7 +31369,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BN119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BT148"/>
   </ignoredErrors>
 </worksheet>
 </file>
